--- a/public/sample_uploads/fund_units_diff_issue_date.xlsx
+++ b/public/sample_uploads/fund_units_diff_issue_date.xlsx
@@ -143,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -166,7 +166,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -189,7 +189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -212,7 +212,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -236,7 +236,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -264,7 +264,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="22">
   <si>
     <t xml:space="preserve">Fund *</t>
   </si>
@@ -278,7 +278,10 @@
     <t xml:space="preserve">Unit Type *</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity *</t>
+    <t xml:space="preserve">Call Quantity *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribution Quantity *</t>
   </si>
   <si>
     <t xml:space="preserve">Price *</t>
@@ -690,7 +693,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J1048576"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="9.06640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
@@ -698,12 +701,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="6.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="34.87"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="1" width="9.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="6.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="34.87"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="1" width="9.06"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -737,177 +740,175 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="G2" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="H2" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="6" t="s">
         <v>14</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>15</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="G3" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="H3" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>14</v>
+      <c r="I3" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>15</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>-25</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="G4" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="H4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>14</v>
+      <c r="I4" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>15</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="n">
         <v>-10</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="G5" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="H5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>14</v>
+      <c r="I5" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>15</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="n">
         <v>-15</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="G6" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="H6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>14</v>
+      <c r="I6" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="K6" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="I2:I1006" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="J2:J1006" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/public/sample_uploads/fund_units_diff_issue_date.xlsx
+++ b/public/sample_uploads/fund_units_diff_issue_date.xlsx
@@ -143,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -166,7 +166,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -189,7 +189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -212,7 +212,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -236,7 +236,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -264,7 +264,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="21">
   <si>
     <t xml:space="preserve">Fund *</t>
   </si>
@@ -278,10 +278,7 @@
     <t xml:space="preserve">Unit Type *</t>
   </si>
   <si>
-    <t xml:space="preserve">Call Quantity *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distribution Quantity *</t>
+    <t xml:space="preserve">Quantity *</t>
   </si>
   <si>
     <t xml:space="preserve">Price *</t>
@@ -693,7 +690,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:J1048576"/>
   <sheetFormatPr defaultColWidth="9.06640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
@@ -701,12 +698,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="6.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="34.87"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="1" width="9.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="6.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="34.87"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="1" width="9.06"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -740,175 +737,177 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>50</v>
       </c>
+      <c r="F2" s="1" t="n">
+        <v>100</v>
+      </c>
       <c r="G2" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="H2" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="H2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>30</v>
       </c>
+      <c r="F3" s="1" t="n">
+        <v>100</v>
+      </c>
       <c r="G3" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="H3" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I3" s="6" t="s">
-        <v>17</v>
+      <c r="H3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>-25</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>-25</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>19</v>
+      <c r="I4" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>-10</v>
+      </c>
       <c r="F5" s="1" t="n">
-        <v>-10</v>
+        <v>100</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="H5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I5" s="6" t="s">
-        <v>20</v>
+      <c r="H5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>-15</v>
+      </c>
       <c r="F6" s="1" t="n">
-        <v>-15</v>
+        <v>100</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="H6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I6" s="6" t="s">
-        <v>21</v>
+      <c r="H6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>16</v>
-      </c>
     </row>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="J2:J1006" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="I2:I1006" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
